--- a/curiculam_ME.xlsx
+++ b/curiculam_ME.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drlak\my_projects\projects_myTimetable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6E04472-3AF9-442F-B224-CBD1C0BAE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE804D9-FF15-47E4-ADC5-3F4F6E9866CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="4005" windowWidth="19290" windowHeight="10755" activeTab="6" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
+    <workbookView xWindow="3720" yWindow="4050" windowWidth="21705" windowHeight="8580" xr2:uid="{7BEB5D9E-8563-4ED7-B850-B47E02154E05}"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
         <v>185</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1245,7 +1245,7 @@
         <v>185</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>2</v>
